--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Final Project\emi-calculator-automation\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D249C918-F2B3-40C7-BE75-23C88E4A33D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1547D873-1233-4766-82E8-4783698A38EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{C06392C3-B2F8-4A4B-BB2F-76D7B47CBD86}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="CarLoan" sheetId="1" r:id="rId1"/>
+    <sheet name="HomeLoan" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -616,7 +616,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D69B3FAA-C463-4541-8731-C2A4FE16588C}">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.7265625" customWidth="1"/>
@@ -637,7 +637,7 @@
     <col min="16" max="16" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -685,6 +685,41 @@
       </c>
       <c r="P1" t="s">
         <v>23</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>5000000</v>
+      </c>
+      <c r="B2">
+        <v>1000000</v>
+      </c>
+      <c r="C2">
+        <v>50000</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>0.25</v>
+      </c>
+      <c r="G2">
+        <v>2000</v>
+      </c>
+      <c r="H2">
+        <v>30000</v>
+      </c>
+      <c r="I2">
+        <v>5000</v>
+      </c>
+      <c r="J2">
+        <v>2500</v>
       </c>
     </row>
   </sheetData>

--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Final Project\emi-calculator-automation\test-data\"/>
     </mc:Choice>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -115,7 +115,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,8 +145,14 @@
       <color indexed="9"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,6 +168,11 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
       </patternFill>
     </fill>
   </fills>
@@ -200,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -208,6 +220,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -547,11 +562,11 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="12.54296875"/>
+    <col min="2" max="2" customWidth="true" width="11.54296875"/>
+    <col min="4" max="4" customWidth="true" width="16.54296875"/>
+    <col min="5" max="5" customWidth="true" width="15.6328125"/>
+    <col min="6" max="6" customWidth="true" width="12.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -578,25 +593,25 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2">
+      <c r="A2" s="0">
         <v>1500000</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>9.5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="E2">
-        <v>131525</v>
-      </c>
-      <c r="F2">
-        <v>131525</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="E2" t="n" s="0">
+        <v>131525.0</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>131525.0</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -619,106 +634,106 @@
   <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" customWidth="1"/>
-    <col min="2" max="2" width="13.1796875" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" customWidth="1"/>
-    <col min="4" max="4" width="11.36328125" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" customWidth="1"/>
-    <col min="6" max="6" width="18.453125" customWidth="1"/>
-    <col min="7" max="7" width="16.54296875" customWidth="1"/>
-    <col min="8" max="8" width="12.7265625" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="19.81640625" customWidth="1"/>
-    <col min="11" max="11" width="19.08984375" customWidth="1"/>
-    <col min="12" max="12" width="16.81640625" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="9.1796875" customWidth="1"/>
-    <col min="15" max="15" width="19.90625" customWidth="1"/>
-    <col min="16" max="16" width="17.54296875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="10.7265625"/>
+    <col min="2" max="2" customWidth="true" width="13.1796875"/>
+    <col min="3" max="3" customWidth="true" width="13.08984375"/>
+    <col min="4" max="4" customWidth="true" width="11.36328125"/>
+    <col min="5" max="5" customWidth="true" width="11.7265625"/>
+    <col min="6" max="6" customWidth="true" width="18.453125"/>
+    <col min="7" max="7" customWidth="true" width="16.54296875"/>
+    <col min="8" max="8" customWidth="true" width="12.7265625"/>
+    <col min="9" max="9" customWidth="true" width="14.0"/>
+    <col min="10" max="10" customWidth="true" width="19.81640625"/>
+    <col min="11" max="11" customWidth="true" width="19.08984375"/>
+    <col min="12" max="12" customWidth="true" width="16.81640625"/>
+    <col min="13" max="13" customWidth="true" width="12.0"/>
+    <col min="14" max="14" customWidth="true" width="9.1796875"/>
+    <col min="15" max="15" customWidth="true" width="19.90625"/>
+    <col min="16" max="16" customWidth="true" width="17.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" t="s" s="0">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2">
+      <c r="A2" s="0">
         <v>5000000</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>1000000</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>50000</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>9</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="0">
         <v>20</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <v>0.25</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="0">
         <v>2000</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>30000</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="0">
         <v>5000</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="0">
         <v>2500</v>
       </c>
     </row>

--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -116,7 +116,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +144,18 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -212,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -223,6 +235,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -611,7 +629,7 @@
       <c r="F2" t="n" s="0">
         <v>131525.0</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="7" t="s">
         <v>8</v>
       </c>
     </row>

--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Final Project\emi-calculator-automation\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1547D873-1233-4766-82E8-4783698A38EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C04F55-0090-4AAA-89AF-F60D38CEFDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{C06392C3-B2F8-4A4B-BB2F-76D7B47CBD86}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -115,8 +115,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,26 +144,8 @@
       <color indexed="9"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -180,11 +161,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="17"/>
       </patternFill>
     </fill>
   </fills>
@@ -224,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -232,15 +208,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -580,11 +547,11 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="12.54296875"/>
-    <col min="2" max="2" customWidth="true" width="11.54296875"/>
-    <col min="4" max="4" customWidth="true" width="16.54296875"/>
-    <col min="5" max="5" customWidth="true" width="15.6328125"/>
-    <col min="6" max="6" customWidth="true" width="12.54296875"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -611,25 +578,25 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="0">
+      <c r="A2">
         <v>1500000</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B2">
         <v>9.5</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="n" s="0">
-        <v>131525.0</v>
-      </c>
-      <c r="F2" t="n" s="0">
-        <v>131525.0</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="E2">
+        <v>131525</v>
+      </c>
+      <c r="F2">
+        <v>131525</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -652,106 +619,106 @@
   <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="10.7265625"/>
-    <col min="2" max="2" customWidth="true" width="13.1796875"/>
-    <col min="3" max="3" customWidth="true" width="13.08984375"/>
-    <col min="4" max="4" customWidth="true" width="11.36328125"/>
-    <col min="5" max="5" customWidth="true" width="11.7265625"/>
-    <col min="6" max="6" customWidth="true" width="18.453125"/>
-    <col min="7" max="7" customWidth="true" width="16.54296875"/>
-    <col min="8" max="8" customWidth="true" width="12.7265625"/>
-    <col min="9" max="9" customWidth="true" width="14.0"/>
-    <col min="10" max="10" customWidth="true" width="19.81640625"/>
-    <col min="11" max="11" customWidth="true" width="19.08984375"/>
-    <col min="12" max="12" customWidth="true" width="16.81640625"/>
-    <col min="13" max="13" customWidth="true" width="12.0"/>
-    <col min="14" max="14" customWidth="true" width="9.1796875"/>
-    <col min="15" max="15" customWidth="true" width="19.90625"/>
-    <col min="16" max="16" customWidth="true" width="17.54296875"/>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" customWidth="1"/>
+    <col min="6" max="6" width="18.453125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="19.81640625" customWidth="1"/>
+    <col min="11" max="11" width="19.08984375" customWidth="1"/>
+    <col min="12" max="12" width="16.81640625" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="9.1796875" customWidth="1"/>
+    <col min="15" max="15" width="19.90625" customWidth="1"/>
+    <col min="16" max="16" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="N1" t="s">
         <v>20</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="O1" t="s">
         <v>21</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="P1" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" t="s" s="0">
+      <c r="Q1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2" s="0">
+      <c r="A2">
         <v>5000000</v>
       </c>
-      <c r="B2" s="0">
-        <v>1000000</v>
-      </c>
-      <c r="C2" s="0">
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
         <v>50000</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>9</v>
       </c>
-      <c r="E2" s="0">
+      <c r="E2">
         <v>20</v>
       </c>
-      <c r="F2" s="0">
+      <c r="F2">
         <v>0.25</v>
       </c>
-      <c r="G2" s="0">
+      <c r="G2">
         <v>2000</v>
       </c>
-      <c r="H2" s="0">
+      <c r="H2">
         <v>30000</v>
       </c>
-      <c r="I2" s="0">
+      <c r="I2">
         <v>5000</v>
       </c>
-      <c r="J2" s="0">
+      <c r="J2">
         <v>2500</v>
       </c>
     </row>

--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Final Project\emi-calculator-automation\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C04F55-0090-4AAA-89AF-F60D38CEFDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21DE24F-3ADB-41BA-B27E-87900A62D18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{C06392C3-B2F8-4A4B-BB2F-76D7B47CBD86}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -90,12 +90,6 @@
     <t>Property Taxes</t>
   </si>
   <si>
-    <t>Expected Loan Amount</t>
-  </si>
-  <si>
-    <t>Actual Loan Amount</t>
-  </si>
-  <si>
     <t>Expected EMI</t>
   </si>
   <si>
@@ -109,13 +103,23 @@
   </si>
   <si>
     <t>Actual Total Payment</t>
+  </si>
+  <si>
+    <t>Test Case Name</t>
+  </si>
+  <si>
+    <t>Home_Loan_Test</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,8 +148,92 @@
       <color indexed="9"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,6 +249,21 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
       </patternFill>
     </fill>
   </fills>
@@ -200,14 +303,56 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -547,11 +692,11 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="12.54296875"/>
+    <col min="2" max="2" customWidth="true" width="11.54296875"/>
+    <col min="4" max="4" customWidth="true" width="16.54296875"/>
+    <col min="5" max="5" customWidth="true" width="15.6328125"/>
+    <col min="6" max="6" customWidth="true" width="12.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -578,25 +723,25 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2">
+      <c r="A2" s="0">
         <v>1500000</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>9.5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="E2">
-        <v>131525</v>
-      </c>
-      <c r="F2">
-        <v>131525</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="E2" t="n" s="0">
+        <v>131525.0</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>131525.0</v>
+      </c>
+      <c r="G2" s="17" t="s">
         <v>8</v>
       </c>
     </row>
@@ -616,113 +761,130 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D69B3FAA-C463-4541-8731-C2A4FE16588C}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" customWidth="1"/>
-    <col min="2" max="2" width="13.1796875" customWidth="1"/>
-    <col min="3" max="3" width="13.08984375" customWidth="1"/>
-    <col min="4" max="4" width="11.36328125" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" customWidth="1"/>
-    <col min="6" max="6" width="18.453125" customWidth="1"/>
-    <col min="7" max="7" width="16.54296875" customWidth="1"/>
-    <col min="8" max="8" width="12.7265625" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="19.81640625" customWidth="1"/>
-    <col min="11" max="11" width="19.08984375" customWidth="1"/>
-    <col min="12" max="12" width="16.81640625" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="9.1796875" customWidth="1"/>
-    <col min="15" max="15" width="19.90625" customWidth="1"/>
-    <col min="16" max="16" width="17.54296875" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="10.7265625"/>
+    <col min="2" max="2" customWidth="true" width="13.1796875"/>
+    <col min="3" max="3" customWidth="true" width="13.08984375"/>
+    <col min="4" max="4" customWidth="true" width="11.36328125"/>
+    <col min="5" max="5" customWidth="true" width="11.7265625"/>
+    <col min="6" max="6" customWidth="true" width="18.453125"/>
+    <col min="7" max="7" customWidth="true" width="16.54296875"/>
+    <col min="8" max="8" customWidth="true" width="12.7265625"/>
+    <col min="9" max="9" customWidth="true" width="14.0"/>
+    <col min="10" max="10" customWidth="true" width="19.81640625"/>
+    <col min="11" max="11" customWidth="true" width="19.08984375"/>
+    <col min="12" max="12" customWidth="true" width="16.81640625"/>
+    <col min="13" max="13" customWidth="true" width="20.54296875"/>
+    <col min="14" max="14" customWidth="true" width="18.1796875"/>
+    <col min="15" max="15" customWidth="true" width="17.90625"/>
+    <col min="16" max="16" customWidth="true" width="6.08984375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="C1" t="s">
+      <c r="L1" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A2" s="0">
+        <v>1000000</v>
+      </c>
+      <c r="B2" s="0">
+        <v>20</v>
+      </c>
+      <c r="C2" s="0">
+        <v>10000</v>
+      </c>
+      <c r="D2" s="0">
+        <v>9</v>
+      </c>
+      <c r="E2" s="0">
+        <v>20</v>
+      </c>
+      <c r="F2" s="0">
+        <v>0.25</v>
+      </c>
+      <c r="G2" s="0">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="H2" s="0">
+        <v>0.25</v>
+      </c>
+      <c r="I2" s="0">
+        <v>0.05</v>
+      </c>
+      <c r="J2" s="0">
+        <v>2500</v>
+      </c>
+      <c r="K2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="Q1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>5000000</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>50000</v>
-      </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>20</v>
-      </c>
-      <c r="F2">
-        <v>0.25</v>
-      </c>
-      <c r="G2">
-        <v>2000</v>
-      </c>
-      <c r="H2">
-        <v>30000</v>
-      </c>
-      <c r="I2">
-        <v>5000</v>
-      </c>
-      <c r="J2">
-        <v>2500</v>
-      </c>
+      <c r="L2" s="0" t="n">
+        <v>7288.0</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <v>7288.0</v>
+      </c>
+      <c r="N2" s="0" t="n">
+        <v>2711644.0</v>
+      </c>
+      <c r="O2" s="0" t="n">
+        <v>2711092.0</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Final Project\emi-calculator-automation\test-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2478621_cognizant_com/Documents/Desktop/team-project/emi-calculator-automation/test-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21DE24F-3ADB-41BA-B27E-87900A62D18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{B21DE24F-3ADB-41BA-B27E-87900A62D18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F740C52-2C36-4F13-AF11-E8DB942FD6E0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{C06392C3-B2F8-4A4B-BB2F-76D7B47CBD86}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="8170" activeTab="1" xr2:uid="{C06392C3-B2F8-4A4B-BB2F-76D7B47CBD86}"/>
   </bookViews>
   <sheets>
     <sheet name="CarLoan" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="26">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -111,15 +111,17 @@
     <t>Home_Loan_Test</t>
   </si>
   <si>
-    <t>FAIL</t>
+    <t>Home_50L_9pct_20yr</t>
+  </si>
+  <si>
+    <t>Home_30L_8.5pct_15yr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,80 +162,8 @@
       <color indexed="9"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -249,21 +179,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
       </patternFill>
     </fill>
   </fills>
@@ -303,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -319,41 +234,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -692,11 +574,11 @@
   <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="12.54296875"/>
-    <col min="2" max="2" customWidth="true" width="11.54296875"/>
-    <col min="4" max="4" customWidth="true" width="16.54296875"/>
-    <col min="5" max="5" customWidth="true" width="15.6328125"/>
-    <col min="6" max="6" customWidth="true" width="12.54296875"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -723,25 +605,25 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="0">
+      <c r="A2">
         <v>1500000</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B2">
         <v>9.5</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="n" s="0">
-        <v>131525.0</v>
-      </c>
-      <c r="F2" t="n" s="0">
-        <v>131525.0</v>
-      </c>
-      <c r="G2" s="17" t="s">
+      <c r="E2">
+        <v>131525</v>
+      </c>
+      <c r="F2">
+        <v>131525</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -761,127 +643,197 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D69B3FAA-C463-4541-8731-C2A4FE16588C}">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="10.7265625"/>
-    <col min="2" max="2" customWidth="true" width="13.1796875"/>
-    <col min="3" max="3" customWidth="true" width="13.08984375"/>
-    <col min="4" max="4" customWidth="true" width="11.36328125"/>
-    <col min="5" max="5" customWidth="true" width="11.7265625"/>
-    <col min="6" max="6" customWidth="true" width="18.453125"/>
-    <col min="7" max="7" customWidth="true" width="16.54296875"/>
-    <col min="8" max="8" customWidth="true" width="12.7265625"/>
-    <col min="9" max="9" customWidth="true" width="14.0"/>
-    <col min="10" max="10" customWidth="true" width="19.81640625"/>
-    <col min="11" max="11" customWidth="true" width="19.08984375"/>
-    <col min="12" max="12" customWidth="true" width="16.81640625"/>
-    <col min="13" max="13" customWidth="true" width="20.54296875"/>
-    <col min="14" max="14" customWidth="true" width="18.1796875"/>
-    <col min="15" max="15" customWidth="true" width="17.90625"/>
-    <col min="16" max="16" customWidth="true" width="6.08984375"/>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" customWidth="1"/>
+    <col min="6" max="6" width="18.453125" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="19.81640625" customWidth="1"/>
+    <col min="11" max="11" width="24.81640625" customWidth="1"/>
+    <col min="12" max="12" width="16.81640625" customWidth="1"/>
+    <col min="13" max="13" width="20.54296875" customWidth="1"/>
+    <col min="14" max="14" width="18.1796875" customWidth="1"/>
+    <col min="15" max="15" width="17.90625" customWidth="1"/>
+    <col min="16" max="16" width="6.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>15</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>22</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="N1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="O1" t="s">
         <v>21</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="P1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="0">
+      <c r="A2">
         <v>1000000</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B2">
         <v>20</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C2">
         <v>10000</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>9</v>
       </c>
-      <c r="E2" s="0">
+      <c r="E2">
         <v>20</v>
       </c>
-      <c r="F2" s="0">
+      <c r="F2">
         <v>0.25</v>
       </c>
-      <c r="G2" s="0">
+      <c r="G2">
         <v>10</v>
       </c>
-      <c r="H2" s="0">
+      <c r="H2">
         <v>0.25</v>
       </c>
-      <c r="I2" s="0">
+      <c r="I2">
         <v>0.05</v>
       </c>
-      <c r="J2" s="0">
+      <c r="J2">
         <v>2500</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="0" t="n">
-        <v>7288.0</v>
-      </c>
-      <c r="M2" s="0" t="n">
-        <v>7288.0</v>
-      </c>
-      <c r="N2" s="0" t="n">
-        <v>2711644.0</v>
-      </c>
-      <c r="O2" s="0" t="n">
-        <v>2711092.0</v>
-      </c>
-      <c r="P2" s="18" t="s">
+      <c r="L2">
+        <v>7288</v>
+      </c>
+      <c r="M2">
+        <v>7288</v>
+      </c>
+      <c r="N2">
+        <v>2711644</v>
+      </c>
+      <c r="O2">
+        <v>2711092</v>
+      </c>
+      <c r="P2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="R2" s="4"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A3" s="7">
+        <v>5000000</v>
+      </c>
+      <c r="B3" s="7">
+        <v>20</v>
+      </c>
+      <c r="C3" s="7">
+        <v>50000</v>
+      </c>
+      <c r="D3" s="7">
+        <v>9</v>
+      </c>
+      <c r="E3" s="7">
+        <v>20</v>
+      </c>
+      <c r="F3" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="G3" s="7">
+        <v>10</v>
+      </c>
+      <c r="H3" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="I3" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="J3" s="7">
+        <v>2500</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>3000000</v>
+      </c>
+      <c r="B4" s="7">
+        <v>25</v>
+      </c>
+      <c r="C4" s="7">
+        <v>30000</v>
+      </c>
+      <c r="D4" s="7">
+        <v>8.5</v>
+      </c>
+      <c r="E4" s="7">
+        <v>15</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="7">
+        <v>8</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="J4" s="7">
+        <v>1500</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Final Project\emi-calculator-automation\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21DE24F-3ADB-41BA-B27E-87900A62D18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A22B89-79D5-44E8-A24F-0F1EF45B0EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{C06392C3-B2F8-4A4B-BB2F-76D7B47CBD86}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -109,9 +109,6 @@
   </si>
   <si>
     <t>Home_Loan_Test</t>
-  </si>
-  <si>
-    <t>FAIL</t>
   </si>
 </sst>
 </file>
@@ -119,7 +116,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,68 +169,8 @@
       <b val="true"/>
       <color indexed="9"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
-      <color indexed="9"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,16 +191,6 @@
     <fill>
       <patternFill patternType="none">
         <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
       </patternFill>
     </fill>
   </fills>
@@ -303,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -322,37 +249,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -741,7 +638,7 @@
       <c r="F2" t="n" s="0">
         <v>131525.0</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="7" t="s">
         <v>8</v>
       </c>
     </row>
@@ -777,7 +674,7 @@
     <col min="11" max="11" customWidth="true" width="19.08984375"/>
     <col min="12" max="12" customWidth="true" width="16.81640625"/>
     <col min="13" max="13" customWidth="true" width="20.54296875"/>
-    <col min="14" max="14" customWidth="true" width="18.1796875"/>
+    <col min="14" max="14" customWidth="true" width="20.26953125"/>
     <col min="15" max="15" customWidth="true" width="17.90625"/>
     <col min="16" max="16" customWidth="true" width="6.08984375"/>
   </cols>
@@ -878,7 +775,7 @@
       <c r="O2" s="0" t="n">
         <v>2711092.0</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="8" t="s">
         <v>8</v>
       </c>
       <c r="R2" s="4"/>

--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>Home_Loan_Test</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
 </sst>
 </file>
@@ -116,7 +119,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,8 +172,26 @@
       <b val="true"/>
       <color indexed="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -191,6 +212,16 @@
     <fill>
       <patternFill patternType="none">
         <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
       </patternFill>
     </fill>
   </fills>
@@ -230,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -250,6 +281,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -638,7 +678,7 @@
       <c r="F2" t="n" s="0">
         <v>131525.0</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="9" t="s">
         <v>8</v>
       </c>
     </row>
@@ -775,7 +815,7 @@
       <c r="O2" s="0" t="n">
         <v>2711092.0</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="11" t="s">
         <v>8</v>
       </c>
       <c r="R2" s="4"/>

--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -119,7 +119,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +159,18 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -261,7 +273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -290,6 +302,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -678,7 +696,7 @@
       <c r="F2" t="n" s="0">
         <v>131525.0</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="12" t="s">
         <v>8</v>
       </c>
     </row>
@@ -815,7 +833,7 @@
       <c r="O2" s="0" t="n">
         <v>2711092.0</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="13" t="s">
         <v>8</v>
       </c>
       <c r="R2" s="4"/>

--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Final Project\emi-calculator-automation\test-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2478719\IdeaProjects\emi-calculator-automation\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A22B89-79D5-44E8-A24F-0F1EF45B0EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34000CC-D5DB-4139-A207-0378D0DBC2B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{C06392C3-B2F8-4A4B-BB2F-76D7B47CBD86}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{C06392C3-B2F8-4A4B-BB2F-76D7B47CBD86}"/>
   </bookViews>
   <sheets>
     <sheet name="CarLoan" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>Home_Loan_Test</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
 </sst>
 </file>
@@ -170,7 +173,7 @@
       <color indexed="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -186,6 +189,11 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
       </patternFill>
     </fill>
     <fill>
@@ -243,7 +251,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">

--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -119,7 +119,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +159,12 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -273,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -308,6 +314,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -696,7 +705,7 @@
       <c r="F2" t="n" s="0">
         <v>131525.0</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="14" t="s">
         <v>8</v>
       </c>
     </row>

--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -119,7 +119,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +159,12 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -279,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -317,6 +323,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -842,7 +851,7 @@
       <c r="O2" s="0" t="n">
         <v>2711092.0</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="P2" s="15" t="s">
         <v>8</v>
       </c>
       <c r="R2" s="4"/>

--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -119,7 +119,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +159,12 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -285,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -326,6 +332,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -851,7 +860,7 @@
       <c r="O2" s="0" t="n">
         <v>2711092.0</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="16" t="s">
         <v>8</v>
       </c>
       <c r="R2" s="4"/>

--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -119,7 +119,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +159,12 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -291,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -335,6 +341,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -860,7 +869,7 @@
       <c r="O2" s="0" t="n">
         <v>2711092.0</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="P2" s="17" t="s">
         <v>8</v>
       </c>
       <c r="R2" s="4"/>

--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
   <si>
     <t>Loan Amount</t>
   </si>
@@ -119,7 +119,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +159,18 @@
       <sz val="11"/>
       <color indexed="9"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -297,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -344,6 +356,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyAlignment="true" applyFill="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -869,7 +887,7 @@
       <c r="O2" s="0" t="n">
         <v>2711092.0</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="P2" s="19" t="s">
         <v>8</v>
       </c>
       <c r="R2" s="4"/>
